--- a/membership_forms/020_gym_membership_extension_form--membership_forms.xlsx
+++ b/membership_forms/020_gym_membership_extension_form--membership_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -742,8 +742,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -771,12 +771,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly', 'value': 'monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly',_'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly', 'value': 'quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'annually',_'value':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Annually', 'value': 'annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -822,12 +822,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Active', 'value': 'active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'suspended',_'value':_'suspended'}</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Suspended', 'value': 'suspended'}</t>
+          <t>Suspended</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Cancelled', 'value': 'cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'expired',_'value':_'expired'}</t>
+          <t>expired</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Expired', 'value': 'expired'}</t>
+          <t>Expired</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'month-to-month',_'value':_'month_to_month'}</t>
+          <t>month-to-month</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Month-to-Month', 'value': 'month_to_month'}</t>
+          <t>Month-to-Month</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'6-month_extension',_'value':_'six_month_extension'}</t>
+          <t>6-month_extension</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '6-Month Extension', 'value': 'six_month_extension'}</t>
+          <t>6-Month Extension</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'credit_card',_'value':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Credit Card', 'value': 'credit_card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'cash',_'value':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Cash', 'value': 'cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'direct_debit',_'value':_'direct_debit'}</t>
+          <t>direct_debit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Direct Debit', 'value': 'direct_debit'}</t>
+          <t>Direct Debit</t>
         </is>
       </c>
     </row>
